--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260904.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260904.xlsx
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>164,000</t>
+          <t>1,181,617</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>1,181,617</t>
+          <t>164,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>855,349</t>
+          <t>1,335,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,335,000</t>
+          <t>855,349</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,998,587</t>
+          <t>999,822</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>999,822</t>
+          <t>1,998,587</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>202609WTEU6F</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>576,000</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>202609WTEU6F</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>576,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,215,000</t>
+          <t>5,707,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,707,000</t>
+          <t>3,215,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,194,441</t>
+          <t>3,472,981</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,472,981</t>
+          <t>1,194,441</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>581,000</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>581,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>389,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>389,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,185,107</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,182,076</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>2,185,107</t>
+          <t>1,182,076</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>4,948,956</t>
+          <t>181,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>319,000</t>
+          <t>290,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>802,000</t>
+          <t>774,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>774,000</t>
+          <t>227,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>290,000</t>
+          <t>802,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>227,000</t>
+          <t>4,948,956</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>181,000</t>
+          <t>319,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>1,556,400</t>
+          <t>496,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>496,000</t>
+          <t>1,556,400</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,001,121</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>1,754,000</t>
+          <t>1,001,121</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>1,754,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>330,000</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>330,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>678,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>678,000</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
